--- a/Fig.4(a).xlsx
+++ b/Fig.4(a).xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Superconductivity\Nb\Mn3Pt_Nb\Raw data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Paper review\Mn3Pt_Nb\Dataset_2\New folder 2\Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -448,7 +448,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>-1.5625</v>
+        <v>1.5625</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>-3.125</v>
+        <v>3.125</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -500,7 +500,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>-4.6875</v>
+        <v>4.6875</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -526,7 +526,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>-6.25</v>
+        <v>6.25</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -552,7 +552,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>-7.8125</v>
+        <v>7.8125</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -578,7 +578,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>-9.375</v>
+        <v>9.375</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -604,7 +604,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>-10.9375</v>
+        <v>10.9375</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -630,7 +630,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>-12.5</v>
+        <v>12.5</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -656,7 +656,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>-14.0625</v>
+        <v>14.0625</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -682,7 +682,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>-15.625</v>
+        <v>15.625</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -708,7 +708,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>-17.1875</v>
+        <v>17.1875</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -734,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>-18.75</v>
+        <v>18.75</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -760,7 +760,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>-20.3125</v>
+        <v>20.3125</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>-21.875</v>
+        <v>21.875</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -812,7 +812,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>-23.4375</v>
+        <v>23.4375</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -838,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -864,7 +864,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>-26.5625</v>
+        <v>26.5625</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -890,7 +890,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>-28.125</v>
+        <v>28.125</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -916,7 +916,7 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>-29.6875</v>
+        <v>29.6875</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>-31.25</v>
+        <v>31.25</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -968,7 +968,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>-32.8125</v>
+        <v>32.8125</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -994,7 +994,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>-34.375</v>
+        <v>34.375</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>-35.9375</v>
+        <v>35.9375</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1046,7 +1046,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>-37.5</v>
+        <v>37.5</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>-39.0625</v>
+        <v>39.0625</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1098,7 +1098,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>-40.625</v>
+        <v>40.625</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>-42.1875</v>
+        <v>42.1875</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1150,7 +1150,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>-43.75</v>
+        <v>43.75</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>-45.3125</v>
+        <v>45.3125</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -1199,10 +1199,10 @@
         <v>46.875</v>
       </c>
       <c r="C36" s="1">
-        <v>-1.0767E-4</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>-46.875</v>
+        <v>46.875</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -1225,10 +1225,10 @@
         <v>48.4375</v>
       </c>
       <c r="C37">
-        <v>-8.3750000000000005E-2</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>-48.4375</v>
+        <v>48.4375</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1251,10 +1251,10 @@
         <v>50</v>
       </c>
       <c r="C38">
-        <v>-8.7660000000000002E-2</v>
+        <v>7.8920000000000004E-2</v>
       </c>
       <c r="D38">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -1277,10 +1277,10 @@
         <v>51.5625</v>
       </c>
       <c r="C39">
-        <v>-9.042E-2</v>
+        <v>9.0440000000000006E-2</v>
       </c>
       <c r="D39">
-        <v>-51.5625</v>
+        <v>51.5625</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -1303,10 +1303,10 @@
         <v>53.125</v>
       </c>
       <c r="C40">
-        <v>-9.3160000000000007E-2</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="D40">
-        <v>-53.125</v>
+        <v>53.125</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -1329,10 +1329,10 @@
         <v>54.6875</v>
       </c>
       <c r="C41">
-        <v>-9.5909999999999995E-2</v>
+        <v>9.5930000000000001E-2</v>
       </c>
       <c r="D41">
-        <v>-54.6875</v>
+        <v>54.6875</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -1355,10 +1355,10 @@
         <v>56.25</v>
       </c>
       <c r="C42">
-        <v>-9.8650000000000002E-2</v>
+        <v>9.8650000000000002E-2</v>
       </c>
       <c r="D42">
-        <v>-56.25</v>
+        <v>56.25</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -1381,10 +1381,10 @@
         <v>57.8125</v>
       </c>
       <c r="C43">
-        <v>-0.1014</v>
+        <v>0.1014</v>
       </c>
       <c r="D43">
-        <v>-57.8125</v>
+        <v>57.8125</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -1407,10 +1407,10 @@
         <v>59.375</v>
       </c>
       <c r="C44">
-        <v>-0.10414</v>
+        <v>0.10414</v>
       </c>
       <c r="D44">
-        <v>-59.375</v>
+        <v>59.375</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -1433,10 +1433,10 @@
         <v>60.9375</v>
       </c>
       <c r="C45">
-        <v>-0.10689</v>
+        <v>0.10689</v>
       </c>
       <c r="D45">
-        <v>-60.9375</v>
+        <v>60.9375</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -1459,10 +1459,10 @@
         <v>62.5</v>
       </c>
       <c r="C46">
-        <v>-0.10963000000000001</v>
+        <v>0.10965</v>
       </c>
       <c r="D46">
-        <v>-62.5</v>
+        <v>62.5</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -1485,10 +1485,10 @@
         <v>64.0625</v>
       </c>
       <c r="C47">
-        <v>-0.11239</v>
+        <v>0.11239</v>
       </c>
       <c r="D47">
-        <v>-64.0625</v>
+        <v>64.0625</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -1511,10 +1511,10 @@
         <v>65.625</v>
       </c>
       <c r="C48">
-        <v>-0.11514000000000001</v>
+        <v>0.11512</v>
       </c>
       <c r="D48">
-        <v>-65.625</v>
+        <v>65.625</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>67.1875</v>
       </c>
       <c r="C49">
-        <v>-0.11788</v>
+        <v>0.11788</v>
       </c>
       <c r="D49">
-        <v>-67.1875</v>
+        <v>67.1875</v>
       </c>
       <c r="E49">
         <v>0.11731</v>
@@ -1563,10 +1563,10 @@
         <v>68.75</v>
       </c>
       <c r="C50">
-        <v>-0.12063</v>
+        <v>0.12060999999999999</v>
       </c>
       <c r="D50">
-        <v>-68.75</v>
+        <v>68.75</v>
       </c>
       <c r="E50">
         <v>0.12028</v>
@@ -1589,10 +1589,10 @@
         <v>70.3125</v>
       </c>
       <c r="C51">
-        <v>-0.12339</v>
+        <v>0.12335</v>
       </c>
       <c r="D51">
-        <v>-70.3125</v>
+        <v>70.3125</v>
       </c>
       <c r="E51">
         <v>0.12324</v>
@@ -1615,10 +1615,10 @@
         <v>71.875</v>
       </c>
       <c r="C52">
-        <v>-0.12612000000000001</v>
+        <v>0.12609999999999999</v>
       </c>
       <c r="D52">
-        <v>-71.875</v>
+        <v>71.875</v>
       </c>
       <c r="E52">
         <v>0.12609999999999999</v>
@@ -1641,10 +1641,10 @@
         <v>73.4375</v>
       </c>
       <c r="C53">
-        <v>-0.12887999999999999</v>
+        <v>0.12886</v>
       </c>
       <c r="D53">
-        <v>-73.4375</v>
+        <v>73.4375</v>
       </c>
       <c r="E53">
         <v>0.12884000000000001</v>
@@ -1667,10 +1667,10 @@
         <v>75</v>
       </c>
       <c r="C54">
-        <v>-0.13161999999999999</v>
+        <v>0.13161999999999999</v>
       </c>
       <c r="D54">
-        <v>-75</v>
+        <v>75</v>
       </c>
       <c r="E54">
         <v>0.13156999999999999</v>
@@ -1693,10 +1693,10 @@
         <v>76.5625</v>
       </c>
       <c r="C55">
-        <v>-0.13435</v>
+        <v>0.13433</v>
       </c>
       <c r="D55">
-        <v>-76.5625</v>
+        <v>76.5625</v>
       </c>
       <c r="E55">
         <v>0.13433</v>
@@ -1719,10 +1719,10 @@
         <v>78.125</v>
       </c>
       <c r="C56">
-        <v>-0.13711000000000001</v>
+        <v>0.13708000000000001</v>
       </c>
       <c r="D56">
-        <v>-78.125</v>
+        <v>78.125</v>
       </c>
       <c r="E56">
         <v>0.13708000000000001</v>
@@ -1745,10 +1745,10 @@
         <v>79.6875</v>
       </c>
       <c r="C57">
-        <v>-0.13986000000000001</v>
+        <v>0.13982</v>
       </c>
       <c r="D57">
-        <v>-79.6875</v>
+        <v>79.6875</v>
       </c>
       <c r="E57">
         <v>0.13982</v>
@@ -1771,10 +1771,10 @@
         <v>81.25</v>
       </c>
       <c r="C58">
-        <v>-0.1426</v>
+        <v>0.14258000000000001</v>
       </c>
       <c r="D58">
-        <v>-81.25</v>
+        <v>81.25</v>
       </c>
       <c r="E58">
         <v>0.14258000000000001</v>
@@ -1797,10 +1797,10 @@
         <v>82.8125</v>
       </c>
       <c r="C59">
-        <v>-0.14538000000000001</v>
+        <v>0.14529</v>
       </c>
       <c r="D59">
-        <v>-82.8125</v>
+        <v>82.8125</v>
       </c>
       <c r="E59">
         <v>0.14530999999999999</v>
@@ -1823,10 +1823,10 @@
         <v>84.375</v>
       </c>
       <c r="C60">
-        <v>-0.14810999999999999</v>
+        <v>0.14804999999999999</v>
       </c>
       <c r="D60">
-        <v>-84.375</v>
+        <v>84.375</v>
       </c>
       <c r="E60">
         <v>0.14807000000000001</v>
@@ -1849,10 +1849,10 @@
         <v>85.9375</v>
       </c>
       <c r="C61">
-        <v>-0.15087</v>
+        <v>0.15079999999999999</v>
       </c>
       <c r="D61">
-        <v>-85.9375</v>
+        <v>85.9375</v>
       </c>
       <c r="E61">
         <v>0.15082000000000001</v>
@@ -1875,10 +1875,10 @@
         <v>87.5</v>
       </c>
       <c r="C62">
-        <v>-0.15362000000000001</v>
+        <v>0.15357999999999999</v>
       </c>
       <c r="D62">
-        <v>-87.5</v>
+        <v>87.5</v>
       </c>
       <c r="E62">
         <v>0.15359999999999999</v>
@@ -1901,10 +1901,10 @@
         <v>89.0625</v>
       </c>
       <c r="C63">
-        <v>-0.15636</v>
+        <v>0.15634000000000001</v>
       </c>
       <c r="D63">
-        <v>-89.0625</v>
+        <v>89.0625</v>
       </c>
       <c r="E63">
         <v>0.15634000000000001</v>
@@ -1927,10 +1927,10 @@
         <v>90.625</v>
       </c>
       <c r="C64">
-        <v>-0.15914</v>
+        <v>0.15909000000000001</v>
       </c>
       <c r="D64">
-        <v>-90.625</v>
+        <v>90.625</v>
       </c>
       <c r="E64">
         <v>0.15906999999999999</v>
@@ -1953,10 +1953,10 @@
         <v>92.1875</v>
       </c>
       <c r="C65">
-        <v>-0.16189000000000001</v>
+        <v>0.16184999999999999</v>
       </c>
       <c r="D65">
-        <v>-92.1875</v>
+        <v>92.1875</v>
       </c>
       <c r="E65">
         <v>0.16183</v>
@@ -1979,10 +1979,10 @@
         <v>93.75</v>
       </c>
       <c r="C66">
-        <v>-0.16464999999999999</v>
+        <v>0.16458</v>
       </c>
       <c r="D66">
-        <v>-93.75</v>
+        <v>93.75</v>
       </c>
       <c r="E66">
         <v>0.16458</v>
@@ -2005,10 +2005,10 @@
         <v>95.3125</v>
       </c>
       <c r="C67">
-        <v>-0.16739999999999999</v>
+        <v>0.16733999999999999</v>
       </c>
       <c r="D67">
-        <v>-95.3125</v>
+        <v>95.3125</v>
       </c>
       <c r="E67">
         <v>0.16732</v>
@@ -2031,10 +2031,10 @@
         <v>96.875</v>
       </c>
       <c r="C68">
-        <v>-0.17016000000000001</v>
+        <v>0.1701</v>
       </c>
       <c r="D68">
-        <v>-96.875</v>
+        <v>96.875</v>
       </c>
       <c r="E68">
         <v>0.1701</v>
@@ -2057,10 +2057,10 @@
         <v>98.4375</v>
       </c>
       <c r="C69">
-        <v>-0.17294000000000001</v>
+        <v>0.17285</v>
       </c>
       <c r="D69">
-        <v>-98.4375</v>
+        <v>98.4375</v>
       </c>
       <c r="E69">
         <v>0.17285</v>
@@ -2083,10 +2083,10 @@
         <v>100</v>
       </c>
       <c r="C70">
-        <v>-0.17533000000000001</v>
+        <v>0.17529</v>
       </c>
       <c r="D70">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="E70">
         <v>0.17524000000000001</v>
@@ -2109,10 +2109,10 @@
         <v>98.4375</v>
       </c>
       <c r="C71">
-        <v>-0.17257</v>
+        <v>0.17252999999999999</v>
       </c>
       <c r="D71">
-        <v>-98.4375</v>
+        <v>98.4375</v>
       </c>
       <c r="E71">
         <v>0.17252999999999999</v>
@@ -2135,10 +2135,10 @@
         <v>96.875</v>
       </c>
       <c r="C72">
-        <v>-0.16982</v>
+        <v>0.16979</v>
       </c>
       <c r="D72">
-        <v>-96.875</v>
+        <v>96.875</v>
       </c>
       <c r="E72">
         <v>0.16972999999999999</v>
@@ -2161,10 +2161,10 @@
         <v>95.3125</v>
       </c>
       <c r="C73">
-        <v>-0.16705999999999999</v>
+        <v>0.16702</v>
       </c>
       <c r="D73">
-        <v>-95.3125</v>
+        <v>95.3125</v>
       </c>
       <c r="E73">
         <v>0.16700000000000001</v>
@@ -2187,10 +2187,10 @@
         <v>93.75</v>
       </c>
       <c r="C74">
-        <v>-0.1643</v>
+        <v>0.1643</v>
       </c>
       <c r="D74">
-        <v>-93.75</v>
+        <v>93.75</v>
       </c>
       <c r="E74">
         <v>0.16424</v>
@@ -2213,10 +2213,10 @@
         <v>92.1875</v>
       </c>
       <c r="C75">
-        <v>-0.16156999999999999</v>
+        <v>0.1615</v>
       </c>
       <c r="D75">
-        <v>-92.1875</v>
+        <v>92.1875</v>
       </c>
       <c r="E75">
         <v>0.1615</v>
@@ -2239,10 +2239,10 @@
         <v>90.625</v>
       </c>
       <c r="C76">
-        <v>-0.15878999999999999</v>
+        <v>0.15876999999999999</v>
       </c>
       <c r="D76">
-        <v>-90.625</v>
+        <v>90.625</v>
       </c>
       <c r="E76">
         <v>0.15873000000000001</v>
@@ -2265,10 +2265,10 @@
         <v>89.0625</v>
       </c>
       <c r="C77">
-        <v>-0.15606</v>
+        <v>0.15598999999999999</v>
       </c>
       <c r="D77">
-        <v>-89.0625</v>
+        <v>89.0625</v>
       </c>
       <c r="E77">
         <v>0.15598999999999999</v>
@@ -2291,10 +2291,10 @@
         <v>87.5</v>
       </c>
       <c r="C78">
-        <v>-0.15329999999999999</v>
+        <v>0.15326000000000001</v>
       </c>
       <c r="D78">
-        <v>-87.5</v>
+        <v>87.5</v>
       </c>
       <c r="E78">
         <v>0.15323999999999999</v>
@@ -2317,10 +2317,10 @@
         <v>85.9375</v>
       </c>
       <c r="C79">
-        <v>-0.15054000000000001</v>
+        <v>0.15048</v>
       </c>
       <c r="D79">
-        <v>-85.9375</v>
+        <v>85.9375</v>
       </c>
       <c r="E79">
         <v>0.15048</v>
@@ -2343,10 +2343,10 @@
         <v>84.375</v>
       </c>
       <c r="C80">
-        <v>-0.14779</v>
+        <v>0.14774000000000001</v>
       </c>
       <c r="D80">
-        <v>-84.375</v>
+        <v>84.375</v>
       </c>
       <c r="E80">
         <v>0.14774000000000001</v>
@@ -2369,10 +2369,10 @@
         <v>82.8125</v>
       </c>
       <c r="C81">
-        <v>-0.14502999999999999</v>
+        <v>0.14499000000000001</v>
       </c>
       <c r="D81">
-        <v>-82.8125</v>
+        <v>82.8125</v>
       </c>
       <c r="E81">
         <v>0.14496999999999999</v>
@@ -2395,10 +2395,10 @@
         <v>81.25</v>
       </c>
       <c r="C82">
-        <v>-0.14230000000000001</v>
+        <v>0.14227000000000001</v>
       </c>
       <c r="D82">
-        <v>-81.25</v>
+        <v>81.25</v>
       </c>
       <c r="E82">
         <v>0.14223</v>
@@ -2421,10 +2421,10 @@
         <v>79.6875</v>
       </c>
       <c r="C83">
-        <v>-0.13954</v>
+        <v>0.13950000000000001</v>
       </c>
       <c r="D83">
-        <v>-79.6875</v>
+        <v>79.6875</v>
       </c>
       <c r="E83">
         <v>0.13950000000000001</v>
@@ -2447,10 +2447,10 @@
         <v>78.125</v>
       </c>
       <c r="C84">
-        <v>-0.1368</v>
+        <v>0.13675999999999999</v>
       </c>
       <c r="D84">
-        <v>-78.125</v>
+        <v>78.125</v>
       </c>
       <c r="E84">
         <v>0.13674</v>
@@ -2473,10 +2473,10 @@
         <v>76.5625</v>
       </c>
       <c r="C85">
-        <v>-0.13403000000000001</v>
+        <v>0.13403000000000001</v>
       </c>
       <c r="D85">
-        <v>-76.5625</v>
+        <v>76.5625</v>
       </c>
       <c r="E85">
         <v>0.13397999999999999</v>
@@ -2499,10 +2499,10 @@
         <v>75</v>
       </c>
       <c r="C86">
-        <v>-0.13128999999999999</v>
+        <v>0.13127</v>
       </c>
       <c r="D86">
-        <v>-75</v>
+        <v>75</v>
       </c>
       <c r="E86">
         <v>0.13125000000000001</v>
@@ -2525,10 +2525,10 @@
         <v>73.4375</v>
       </c>
       <c r="C87">
-        <v>-0.12856000000000001</v>
+        <v>0.12856000000000001</v>
       </c>
       <c r="D87">
-        <v>-73.4375</v>
+        <v>73.4375</v>
       </c>
       <c r="E87">
         <v>0.12851000000000001</v>
@@ -2551,10 +2551,10 @@
         <v>71.875</v>
       </c>
       <c r="C88">
-        <v>-0.1258</v>
+        <v>0.12578</v>
       </c>
       <c r="D88">
-        <v>-71.875</v>
+        <v>71.875</v>
       </c>
       <c r="E88">
         <v>0.12576000000000001</v>
@@ -2577,10 +2577,10 @@
         <v>70.3125</v>
       </c>
       <c r="C89">
-        <v>-0.12304</v>
+        <v>0.12307</v>
       </c>
       <c r="D89">
-        <v>-70.3125</v>
+        <v>70.3125</v>
       </c>
       <c r="E89">
         <v>0.123</v>
@@ -2603,10 +2603,10 @@
         <v>68.75</v>
       </c>
       <c r="C90">
-        <v>-0.12033000000000001</v>
+        <v>0.12031</v>
       </c>
       <c r="D90">
-        <v>-68.75</v>
+        <v>68.75</v>
       </c>
       <c r="E90">
         <v>0.12027</v>
@@ -2629,10 +2629,10 @@
         <v>67.1875</v>
       </c>
       <c r="C91">
-        <v>-0.11755</v>
+        <v>0.11758</v>
       </c>
       <c r="D91">
-        <v>-67.1875</v>
+        <v>67.1875</v>
       </c>
       <c r="E91">
         <v>0.11753</v>
@@ -2655,10 +2655,10 @@
         <v>65.625</v>
       </c>
       <c r="C92">
-        <v>-0.11482000000000001</v>
+        <v>0.11484</v>
       </c>
       <c r="D92">
-        <v>-65.625</v>
+        <v>65.625</v>
       </c>
       <c r="E92">
         <v>0.11477999999999999</v>
@@ -2681,10 +2681,10 @@
         <v>64.0625</v>
       </c>
       <c r="C93">
-        <v>-0.11206000000000001</v>
+        <v>0.11211</v>
       </c>
       <c r="D93">
-        <v>-64.0625</v>
+        <v>64.0625</v>
       </c>
       <c r="E93">
         <v>0.11204</v>
@@ -2707,10 +2707,10 @@
         <v>62.5</v>
       </c>
       <c r="C94">
-        <v>-0.10931</v>
+        <v>0.10931</v>
       </c>
       <c r="D94">
-        <v>-62.5</v>
+        <v>62.5</v>
       </c>
       <c r="E94">
         <v>0.10928</v>
@@ -2733,10 +2733,10 @@
         <v>60.9375</v>
       </c>
       <c r="C95">
-        <v>-0.10657</v>
+        <v>0.10661</v>
       </c>
       <c r="D95">
-        <v>-60.9375</v>
+        <v>60.9375</v>
       </c>
       <c r="E95">
         <v>0.10653</v>
@@ -2759,10 +2759,10 @@
         <v>59.375</v>
       </c>
       <c r="C96">
-        <v>-0.10384</v>
+        <v>0.10384</v>
       </c>
       <c r="D96">
-        <v>-59.375</v>
+        <v>59.375</v>
       </c>
       <c r="E96">
         <v>0.10378999999999999</v>
@@ -2785,10 +2785,10 @@
         <v>57.8125</v>
       </c>
       <c r="C97">
-        <v>-0.10108</v>
+        <v>0.10112</v>
       </c>
       <c r="D97">
-        <v>-57.8125</v>
+        <v>57.8125</v>
       </c>
       <c r="E97">
         <v>0.10104</v>
@@ -2811,10 +2811,10 @@
         <v>56.25</v>
       </c>
       <c r="C98">
-        <v>-9.8350000000000007E-2</v>
+        <v>9.8369999999999999E-2</v>
       </c>
       <c r="D98">
-        <v>-56.25</v>
+        <v>56.25</v>
       </c>
       <c r="E98">
         <v>9.8299999999999998E-2</v>
@@ -2837,10 +2837,10 @@
         <v>54.6875</v>
       </c>
       <c r="C99">
-        <v>-9.5589999999999994E-2</v>
+        <v>9.5649999999999999E-2</v>
       </c>
       <c r="D99">
-        <v>-54.6875</v>
+        <v>54.6875</v>
       </c>
       <c r="E99">
         <v>9.5570000000000002E-2</v>
@@ -2863,10 +2863,10 @@
         <v>53.125</v>
       </c>
       <c r="C100">
-        <v>-9.2850000000000002E-2</v>
+        <v>9.2899999999999996E-2</v>
       </c>
       <c r="D100">
-        <v>-53.125</v>
+        <v>53.125</v>
       </c>
       <c r="E100">
         <v>9.2829999999999996E-2</v>
@@ -2889,10 +2889,10 @@
         <v>51.5625</v>
       </c>
       <c r="C101">
-        <v>-9.0120000000000006E-2</v>
+        <v>9.0160000000000004E-2</v>
       </c>
       <c r="D101">
-        <v>-51.5625</v>
+        <v>51.5625</v>
       </c>
       <c r="E101">
         <v>9.0079999999999993E-2</v>
@@ -2915,10 +2915,10 @@
         <v>50</v>
       </c>
       <c r="C102">
-        <v>-8.7279999999999996E-2</v>
+        <v>8.7340000000000001E-2</v>
       </c>
       <c r="D102">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="E102">
         <v>8.7260000000000004E-2</v>
@@ -2941,10 +2941,10 @@
         <v>48.4375</v>
       </c>
       <c r="C103">
-        <v>-8.4540000000000004E-2</v>
+        <v>8.4610000000000005E-2</v>
       </c>
       <c r="D103">
-        <v>-48.4375</v>
+        <v>48.4375</v>
       </c>
       <c r="E103">
         <v>8.4519999999999998E-2</v>
@@ -2967,10 +2967,10 @@
         <v>46.875</v>
       </c>
       <c r="C104">
-        <v>-8.1790000000000002E-2</v>
+        <v>8.1850000000000006E-2</v>
       </c>
       <c r="D104">
-        <v>-46.875</v>
+        <v>46.875</v>
       </c>
       <c r="E104">
         <v>8.1759999999999999E-2</v>
@@ -2993,10 +2993,10 @@
         <v>45.3125</v>
       </c>
       <c r="C105">
-        <v>-7.9030000000000003E-2</v>
+        <v>7.9140000000000002E-2</v>
       </c>
       <c r="D105">
-        <v>-45.3125</v>
+        <v>45.3125</v>
       </c>
       <c r="E105">
         <v>7.9049999999999995E-2</v>
@@ -3019,10 +3019,10 @@
         <v>43.75</v>
       </c>
       <c r="C106">
-        <v>-7.6289999999999997E-2</v>
+        <v>7.6380000000000003E-2</v>
       </c>
       <c r="D106">
-        <v>-43.75</v>
+        <v>43.75</v>
       </c>
       <c r="E106">
         <v>7.6270000000000004E-2</v>
@@ -3045,10 +3045,10 @@
         <v>42.1875</v>
       </c>
       <c r="C107">
-        <v>-7.356E-2</v>
+        <v>7.3649999999999993E-2</v>
       </c>
       <c r="D107">
-        <v>-42.1875</v>
+        <v>42.1875</v>
       </c>
       <c r="E107">
         <v>7.356E-2</v>
@@ -3071,10 +3071,10 @@
         <v>40.625</v>
       </c>
       <c r="C108">
-        <v>-7.0800000000000002E-2</v>
+        <v>7.0889999999999995E-2</v>
       </c>
       <c r="D108">
-        <v>-40.625</v>
+        <v>40.625</v>
       </c>
       <c r="E108">
         <v>7.0800000000000002E-2</v>
@@ -3097,10 +3097,10 @@
         <v>39.0625</v>
       </c>
       <c r="C109">
-        <v>-6.8070000000000006E-2</v>
+        <v>6.8180000000000004E-2</v>
       </c>
       <c r="D109">
-        <v>-39.0625</v>
+        <v>39.0625</v>
       </c>
       <c r="E109">
         <v>6.8049999999999999E-2</v>
@@ -3123,10 +3123,10 @@
         <v>37.5</v>
       </c>
       <c r="C110">
-        <v>-6.5310000000000007E-2</v>
+        <v>6.54E-2</v>
       </c>
       <c r="D110">
-        <v>-37.5</v>
+        <v>37.5</v>
       </c>
       <c r="E110">
         <v>6.5180000000000002E-2</v>
@@ -3149,10 +3149,10 @@
         <v>35.9375</v>
       </c>
       <c r="C111">
-        <v>-6.2579999999999997E-2</v>
+        <v>6.2689999999999996E-2</v>
       </c>
       <c r="D111">
-        <v>-35.9375</v>
+        <v>35.9375</v>
       </c>
       <c r="E111">
         <v>6.1310000000000003E-2</v>
@@ -3175,10 +3175,10 @@
         <v>34.375</v>
       </c>
       <c r="C112">
-        <v>-5.9819999999999998E-2</v>
+        <v>5.9909999999999998E-2</v>
       </c>
       <c r="D112">
-        <v>-34.375</v>
+        <v>34.375</v>
       </c>
       <c r="E112">
         <v>5.2650000000000002E-2</v>
@@ -3201,10 +3201,10 @@
         <v>32.8125</v>
       </c>
       <c r="C113">
-        <v>-5.706E-2</v>
+        <v>5.7169999999999999E-2</v>
       </c>
       <c r="D113">
-        <v>-32.8125</v>
+        <v>32.8125</v>
       </c>
       <c r="E113">
         <v>2.48E-3</v>
@@ -3227,10 +3227,10 @@
         <v>31.25</v>
       </c>
       <c r="C114">
-        <v>-5.4179999999999999E-2</v>
+        <v>5.416E-2</v>
       </c>
       <c r="D114">
-        <v>-31.25</v>
+        <v>31.25</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -3253,10 +3253,10 @@
         <v>29.6875</v>
       </c>
       <c r="C115">
-        <v>-5.0650000000000001E-2</v>
+        <v>5.0070000000000003E-2</v>
       </c>
       <c r="D115">
-        <v>-29.6875</v>
+        <v>29.6875</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -3279,10 +3279,10 @@
         <v>28.125</v>
       </c>
       <c r="C116">
-        <v>-4.5289999999999997E-2</v>
+        <v>4.3580000000000001E-2</v>
       </c>
       <c r="D116">
-        <v>-28.125</v>
+        <v>28.125</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -3305,10 +3305,10 @@
         <v>26.5625</v>
       </c>
       <c r="C117">
-        <v>-3.6799999999999999E-2</v>
+        <v>1.3440000000000001E-2</v>
       </c>
       <c r="D117">
-        <v>-26.5625</v>
+        <v>26.5625</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -3331,10 +3331,10 @@
         <v>25</v>
       </c>
       <c r="C118">
-        <v>-5.1000000000000004E-3</v>
+        <v>0</v>
       </c>
       <c r="D118">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -3360,7 +3360,7 @@
         <v>0</v>
       </c>
       <c r="D119">
-        <v>-23.4375</v>
+        <v>23.4375</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="D120">
-        <v>-21.875</v>
+        <v>21.875</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -3412,7 +3412,7 @@
         <v>0</v>
       </c>
       <c r="D121">
-        <v>-20.3125</v>
+        <v>20.3125</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -3438,7 +3438,7 @@
         <v>0</v>
       </c>
       <c r="D122">
-        <v>-18.75</v>
+        <v>18.75</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -3464,7 +3464,7 @@
         <v>0</v>
       </c>
       <c r="D123">
-        <v>-17.1875</v>
+        <v>17.1875</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -3490,7 +3490,7 @@
         <v>0</v>
       </c>
       <c r="D124">
-        <v>-15.625</v>
+        <v>15.625</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -3516,7 +3516,7 @@
         <v>0</v>
       </c>
       <c r="D125">
-        <v>-14.0625</v>
+        <v>14.0625</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -3542,7 +3542,7 @@
         <v>0</v>
       </c>
       <c r="D126">
-        <v>-12.5</v>
+        <v>12.5</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -3568,7 +3568,7 @@
         <v>0</v>
       </c>
       <c r="D127">
-        <v>-10.9375</v>
+        <v>10.9375</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -3594,7 +3594,7 @@
         <v>0</v>
       </c>
       <c r="D128">
-        <v>-9.375</v>
+        <v>9.375</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -3620,7 +3620,7 @@
         <v>0</v>
       </c>
       <c r="D129">
-        <v>-7.8125</v>
+        <v>7.8125</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>0</v>
       </c>
       <c r="D130">
-        <v>-6.25</v>
+        <v>6.25</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -3672,7 +3672,7 @@
         <v>0</v>
       </c>
       <c r="D131">
-        <v>-4.6875</v>
+        <v>4.6875</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -3698,7 +3698,7 @@
         <v>0</v>
       </c>
       <c r="D132">
-        <v>-3.125</v>
+        <v>3.125</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -3724,7 +3724,7 @@
         <v>0</v>
       </c>
       <c r="D133">
-        <v>-1.5625</v>
+        <v>1.5625</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -3776,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="D135">
-        <v>1.5625</v>
+        <v>-1.5625</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -3802,7 +3802,7 @@
         <v>0</v>
       </c>
       <c r="D136">
-        <v>3.125</v>
+        <v>-3.125</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -3828,7 +3828,7 @@
         <v>0</v>
       </c>
       <c r="D137">
-        <v>4.6875</v>
+        <v>-4.6875</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -3854,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="D138">
-        <v>6.25</v>
+        <v>-6.25</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -3880,7 +3880,7 @@
         <v>0</v>
       </c>
       <c r="D139">
-        <v>7.8125</v>
+        <v>-7.8125</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -3906,7 +3906,7 @@
         <v>0</v>
       </c>
       <c r="D140">
-        <v>9.375</v>
+        <v>-9.375</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -3932,7 +3932,7 @@
         <v>0</v>
       </c>
       <c r="D141">
-        <v>10.9375</v>
+        <v>-10.9375</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -3958,7 +3958,7 @@
         <v>0</v>
       </c>
       <c r="D142">
-        <v>12.5</v>
+        <v>-12.5</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -3984,7 +3984,7 @@
         <v>0</v>
       </c>
       <c r="D143">
-        <v>14.0625</v>
+        <v>-14.0625</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -4010,7 +4010,7 @@
         <v>0</v>
       </c>
       <c r="D144">
-        <v>15.625</v>
+        <v>-15.625</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -4036,7 +4036,7 @@
         <v>0</v>
       </c>
       <c r="D145">
-        <v>17.1875</v>
+        <v>-17.1875</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -4062,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="D146">
-        <v>18.75</v>
+        <v>-18.75</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="D147">
-        <v>20.3125</v>
+        <v>-20.3125</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -4114,7 +4114,7 @@
         <v>0</v>
       </c>
       <c r="D148">
-        <v>21.875</v>
+        <v>-21.875</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -4140,7 +4140,7 @@
         <v>0</v>
       </c>
       <c r="D149">
-        <v>23.4375</v>
+        <v>-23.4375</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -4166,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="D150">
-        <v>25</v>
+        <v>-25</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -4192,7 +4192,7 @@
         <v>0</v>
       </c>
       <c r="D151">
-        <v>26.5625</v>
+        <v>-26.5625</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -4218,7 +4218,7 @@
         <v>0</v>
       </c>
       <c r="D152">
-        <v>28.125</v>
+        <v>-28.125</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -4244,7 +4244,7 @@
         <v>0</v>
       </c>
       <c r="D153">
-        <v>29.6875</v>
+        <v>-29.6875</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -4270,7 +4270,7 @@
         <v>0</v>
       </c>
       <c r="D154">
-        <v>31.25</v>
+        <v>-31.25</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -4296,7 +4296,7 @@
         <v>0</v>
       </c>
       <c r="D155">
-        <v>32.8125</v>
+        <v>-32.8125</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -4322,7 +4322,7 @@
         <v>0</v>
       </c>
       <c r="D156">
-        <v>34.375</v>
+        <v>-34.375</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -4348,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="D157">
-        <v>35.9375</v>
+        <v>-35.9375</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -4374,7 +4374,7 @@
         <v>0</v>
       </c>
       <c r="D158">
-        <v>37.5</v>
+        <v>-37.5</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="D159">
-        <v>39.0625</v>
+        <v>-39.0625</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -4426,7 +4426,7 @@
         <v>0</v>
       </c>
       <c r="D160">
-        <v>40.625</v>
+        <v>-40.625</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -4452,7 +4452,7 @@
         <v>0</v>
       </c>
       <c r="D161">
-        <v>42.1875</v>
+        <v>-42.1875</v>
       </c>
       <c r="E161">
         <v>0</v>
@@ -4478,7 +4478,7 @@
         <v>0</v>
       </c>
       <c r="D162">
-        <v>43.75</v>
+        <v>-43.75</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -4504,7 +4504,7 @@
         <v>0</v>
       </c>
       <c r="D163">
-        <v>45.3125</v>
+        <v>-45.3125</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -4526,11 +4526,11 @@
       <c r="B164">
         <v>-46.875</v>
       </c>
-      <c r="C164">
-        <v>0</v>
+      <c r="C164" s="1">
+        <v>-1.0767E-4</v>
       </c>
       <c r="D164">
-        <v>46.875</v>
+        <v>-46.875</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -4553,10 +4553,10 @@
         <v>-48.4375</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>-8.3750000000000005E-2</v>
       </c>
       <c r="D165">
-        <v>48.4375</v>
+        <v>-48.4375</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -4579,10 +4579,10 @@
         <v>-50</v>
       </c>
       <c r="C166">
-        <v>7.8920000000000004E-2</v>
+        <v>-8.7660000000000002E-2</v>
       </c>
       <c r="D166">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -4605,10 +4605,10 @@
         <v>-51.5625</v>
       </c>
       <c r="C167">
-        <v>9.0440000000000006E-2</v>
+        <v>-9.042E-2</v>
       </c>
       <c r="D167">
-        <v>51.5625</v>
+        <v>-51.5625</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>-53.125</v>
       </c>
       <c r="C168">
-        <v>9.3200000000000005E-2</v>
+        <v>-9.3160000000000007E-2</v>
       </c>
       <c r="D168">
-        <v>53.125</v>
+        <v>-53.125</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -4657,10 +4657,10 @@
         <v>-54.6875</v>
       </c>
       <c r="C169">
-        <v>9.5930000000000001E-2</v>
+        <v>-9.5909999999999995E-2</v>
       </c>
       <c r="D169">
-        <v>54.6875</v>
+        <v>-54.6875</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -4683,10 +4683,10 @@
         <v>-56.25</v>
       </c>
       <c r="C170">
-        <v>9.8650000000000002E-2</v>
+        <v>-9.8650000000000002E-2</v>
       </c>
       <c r="D170">
-        <v>56.25</v>
+        <v>-56.25</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -4709,10 +4709,10 @@
         <v>-57.8125</v>
       </c>
       <c r="C171">
-        <v>0.1014</v>
+        <v>-0.1014</v>
       </c>
       <c r="D171">
-        <v>57.8125</v>
+        <v>-57.8125</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -4735,10 +4735,10 @@
         <v>-59.375</v>
       </c>
       <c r="C172">
-        <v>0.10414</v>
+        <v>-0.10414</v>
       </c>
       <c r="D172">
-        <v>59.375</v>
+        <v>-59.375</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -4761,10 +4761,10 @@
         <v>-60.9375</v>
       </c>
       <c r="C173">
-        <v>0.10689</v>
+        <v>-0.10689</v>
       </c>
       <c r="D173">
-        <v>60.9375</v>
+        <v>-60.9375</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -4787,10 +4787,10 @@
         <v>-62.5</v>
       </c>
       <c r="C174">
-        <v>0.10965</v>
+        <v>-0.10963000000000001</v>
       </c>
       <c r="D174">
-        <v>62.5</v>
+        <v>-62.5</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -4813,10 +4813,10 @@
         <v>-64.0625</v>
       </c>
       <c r="C175">
-        <v>0.11239</v>
+        <v>-0.11239</v>
       </c>
       <c r="D175">
-        <v>64.0625</v>
+        <v>-64.0625</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -4839,10 +4839,10 @@
         <v>-65.625</v>
       </c>
       <c r="C176">
-        <v>0.11512</v>
+        <v>-0.11514000000000001</v>
       </c>
       <c r="D176">
-        <v>65.625</v>
+        <v>-65.625</v>
       </c>
       <c r="E176">
         <v>-0.11466999999999999</v>
@@ -4865,10 +4865,10 @@
         <v>-67.1875</v>
       </c>
       <c r="C177">
-        <v>0.11788</v>
+        <v>-0.11788</v>
       </c>
       <c r="D177">
-        <v>67.1875</v>
+        <v>-67.1875</v>
       </c>
       <c r="E177">
         <v>-0.11755</v>
@@ -4891,10 +4891,10 @@
         <v>-68.75</v>
       </c>
       <c r="C178">
-        <v>0.12060999999999999</v>
+        <v>-0.12063</v>
       </c>
       <c r="D178">
-        <v>68.75</v>
+        <v>-68.75</v>
       </c>
       <c r="E178">
         <v>-0.12007</v>
@@ -4917,10 +4917,10 @@
         <v>-70.3125</v>
       </c>
       <c r="C179">
-        <v>0.12335</v>
+        <v>-0.12339</v>
       </c>
       <c r="D179">
-        <v>70.3125</v>
+        <v>-70.3125</v>
       </c>
       <c r="E179">
         <v>-0.12331</v>
@@ -4943,10 +4943,10 @@
         <v>-71.875</v>
       </c>
       <c r="C180">
-        <v>0.12609999999999999</v>
+        <v>-0.12612000000000001</v>
       </c>
       <c r="D180">
-        <v>71.875</v>
+        <v>-71.875</v>
       </c>
       <c r="E180">
         <v>-0.12583</v>
@@ -4969,10 +4969,10 @@
         <v>-73.4375</v>
       </c>
       <c r="C181">
-        <v>0.12886</v>
+        <v>-0.12887999999999999</v>
       </c>
       <c r="D181">
-        <v>73.4375</v>
+        <v>-73.4375</v>
       </c>
       <c r="E181">
         <v>-0.12887999999999999</v>
@@ -4995,10 +4995,10 @@
         <v>-75</v>
       </c>
       <c r="C182">
-        <v>0.13161999999999999</v>
+        <v>-0.13161999999999999</v>
       </c>
       <c r="D182">
-        <v>75</v>
+        <v>-75</v>
       </c>
       <c r="E182">
         <v>-0.13164000000000001</v>
@@ -5021,10 +5021,10 @@
         <v>-76.5625</v>
       </c>
       <c r="C183">
-        <v>0.13433</v>
+        <v>-0.13435</v>
       </c>
       <c r="D183">
-        <v>76.5625</v>
+        <v>-76.5625</v>
       </c>
       <c r="E183">
         <v>-0.13435</v>
@@ -5047,10 +5047,10 @@
         <v>-78.125</v>
       </c>
       <c r="C184">
-        <v>0.13708000000000001</v>
+        <v>-0.13711000000000001</v>
       </c>
       <c r="D184">
-        <v>78.125</v>
+        <v>-78.125</v>
       </c>
       <c r="E184">
         <v>-0.13711000000000001</v>
@@ -5073,10 +5073,10 @@
         <v>-79.6875</v>
       </c>
       <c r="C185">
-        <v>0.13982</v>
+        <v>-0.13986000000000001</v>
       </c>
       <c r="D185">
-        <v>79.6875</v>
+        <v>-79.6875</v>
       </c>
       <c r="E185">
         <v>-0.13986000000000001</v>
@@ -5099,10 +5099,10 @@
         <v>-81.25</v>
       </c>
       <c r="C186">
-        <v>0.14258000000000001</v>
+        <v>-0.1426</v>
       </c>
       <c r="D186">
-        <v>81.25</v>
+        <v>-81.25</v>
       </c>
       <c r="E186">
         <v>-0.1426</v>
@@ -5125,10 +5125,10 @@
         <v>-82.8125</v>
       </c>
       <c r="C187">
-        <v>0.14529</v>
+        <v>-0.14538000000000001</v>
       </c>
       <c r="D187">
-        <v>82.8125</v>
+        <v>-82.8125</v>
       </c>
       <c r="E187">
         <v>-0.14535000000000001</v>
@@ -5151,10 +5151,10 @@
         <v>-84.375</v>
       </c>
       <c r="C188">
-        <v>0.14804999999999999</v>
+        <v>-0.14810999999999999</v>
       </c>
       <c r="D188">
-        <v>84.375</v>
+        <v>-84.375</v>
       </c>
       <c r="E188">
         <v>-0.14809</v>
@@ -5177,10 +5177,10 @@
         <v>-85.9375</v>
       </c>
       <c r="C189">
-        <v>0.15079999999999999</v>
+        <v>-0.15087</v>
       </c>
       <c r="D189">
-        <v>85.9375</v>
+        <v>-85.9375</v>
       </c>
       <c r="E189">
         <v>-0.15087</v>
@@ -5203,10 +5203,10 @@
         <v>-87.5</v>
       </c>
       <c r="C190">
-        <v>0.15357999999999999</v>
+        <v>-0.15362000000000001</v>
       </c>
       <c r="D190">
-        <v>87.5</v>
+        <v>-87.5</v>
       </c>
       <c r="E190">
         <v>-0.15359999999999999</v>
@@ -5229,10 +5229,10 @@
         <v>-89.0625</v>
       </c>
       <c r="C191">
-        <v>0.15634000000000001</v>
+        <v>-0.15636</v>
       </c>
       <c r="D191">
-        <v>89.0625</v>
+        <v>-89.0625</v>
       </c>
       <c r="E191">
         <v>-0.15636</v>
@@ -5255,10 +5255,10 @@
         <v>-90.625</v>
       </c>
       <c r="C192">
-        <v>0.15909000000000001</v>
+        <v>-0.15914</v>
       </c>
       <c r="D192">
-        <v>90.625</v>
+        <v>-90.625</v>
       </c>
       <c r="E192">
         <v>-0.15911</v>
@@ -5281,10 +5281,10 @@
         <v>-92.1875</v>
       </c>
       <c r="C193">
-        <v>0.16184999999999999</v>
+        <v>-0.16189000000000001</v>
       </c>
       <c r="D193">
-        <v>92.1875</v>
+        <v>-92.1875</v>
       </c>
       <c r="E193">
         <v>-0.16187000000000001</v>
@@ -5307,10 +5307,10 @@
         <v>-93.75</v>
       </c>
       <c r="C194">
-        <v>0.16458</v>
+        <v>-0.16464999999999999</v>
       </c>
       <c r="D194">
-        <v>93.75</v>
+        <v>-93.75</v>
       </c>
       <c r="E194">
         <v>-0.16463</v>
@@ -5333,10 +5333,10 @@
         <v>-95.3125</v>
       </c>
       <c r="C195">
-        <v>0.16733999999999999</v>
+        <v>-0.16739999999999999</v>
       </c>
       <c r="D195">
-        <v>95.3125</v>
+        <v>-95.3125</v>
       </c>
       <c r="E195">
         <v>-0.16736000000000001</v>
@@ -5359,10 +5359,10 @@
         <v>-96.875</v>
       </c>
       <c r="C196">
-        <v>0.1701</v>
+        <v>-0.17016000000000001</v>
       </c>
       <c r="D196">
-        <v>96.875</v>
+        <v>-96.875</v>
       </c>
       <c r="E196">
         <v>-0.17011999999999999</v>
@@ -5385,10 +5385,10 @@
         <v>-98.4375</v>
       </c>
       <c r="C197">
-        <v>0.17285</v>
+        <v>-0.17294000000000001</v>
       </c>
       <c r="D197">
-        <v>98.4375</v>
+        <v>-98.4375</v>
       </c>
       <c r="E197">
         <v>-0.1729</v>
@@ -5411,10 +5411,10 @@
         <v>-100</v>
       </c>
       <c r="C198">
-        <v>0.17529</v>
+        <v>-0.17533000000000001</v>
       </c>
       <c r="D198">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="E198">
         <v>-0.17530999999999999</v>
@@ -5437,10 +5437,10 @@
         <v>-98.4375</v>
       </c>
       <c r="C199">
-        <v>0.17252999999999999</v>
+        <v>-0.17257</v>
       </c>
       <c r="D199">
-        <v>98.4375</v>
+        <v>-98.4375</v>
       </c>
       <c r="E199">
         <v>-0.17257</v>
@@ -5463,10 +5463,10 @@
         <v>-96.875</v>
       </c>
       <c r="C200">
-        <v>0.16979</v>
+        <v>-0.16982</v>
       </c>
       <c r="D200">
-        <v>96.875</v>
+        <v>-96.875</v>
       </c>
       <c r="E200">
         <v>-0.16979</v>
@@ -5489,10 +5489,10 @@
         <v>-95.3125</v>
       </c>
       <c r="C201">
-        <v>0.16702</v>
+        <v>-0.16705999999999999</v>
       </c>
       <c r="D201">
-        <v>95.3125</v>
+        <v>-95.3125</v>
       </c>
       <c r="E201">
         <v>-0.16705999999999999</v>
@@ -5515,10 +5515,10 @@
         <v>-93.75</v>
       </c>
       <c r="C202">
-        <v>0.1643</v>
+        <v>-0.1643</v>
       </c>
       <c r="D202">
-        <v>93.75</v>
+        <v>-93.75</v>
       </c>
       <c r="E202">
         <v>-0.1643</v>
@@ -5541,10 +5541,10 @@
         <v>-92.1875</v>
       </c>
       <c r="C203">
-        <v>0.1615</v>
+        <v>-0.16156999999999999</v>
       </c>
       <c r="D203">
-        <v>92.1875</v>
+        <v>-92.1875</v>
       </c>
       <c r="E203">
         <v>-0.16155</v>
@@ -5567,10 +5567,10 @@
         <v>-90.625</v>
       </c>
       <c r="C204">
-        <v>0.15876999999999999</v>
+        <v>-0.15878999999999999</v>
       </c>
       <c r="D204">
-        <v>90.625</v>
+        <v>-90.625</v>
       </c>
       <c r="E204">
         <v>-0.15878999999999999</v>
@@ -5593,10 +5593,10 @@
         <v>-89.0625</v>
       </c>
       <c r="C205">
-        <v>0.15598999999999999</v>
+        <v>-0.15606</v>
       </c>
       <c r="D205">
-        <v>89.0625</v>
+        <v>-89.0625</v>
       </c>
       <c r="E205">
         <v>-0.15603</v>
@@ -5619,10 +5619,10 @@
         <v>-87.5</v>
       </c>
       <c r="C206">
-        <v>0.15326000000000001</v>
+        <v>-0.15329999999999999</v>
       </c>
       <c r="D206">
-        <v>87.5</v>
+        <v>-87.5</v>
       </c>
       <c r="E206">
         <v>-0.15328</v>
@@ -5645,10 +5645,10 @@
         <v>-85.9375</v>
       </c>
       <c r="C207">
-        <v>0.15048</v>
+        <v>-0.15054000000000001</v>
       </c>
       <c r="D207">
-        <v>85.9375</v>
+        <v>-85.9375</v>
       </c>
       <c r="E207">
         <v>-0.15051999999999999</v>
@@ -5671,10 +5671,10 @@
         <v>-84.375</v>
       </c>
       <c r="C208">
-        <v>0.14774000000000001</v>
+        <v>-0.14779</v>
       </c>
       <c r="D208">
-        <v>84.375</v>
+        <v>-84.375</v>
       </c>
       <c r="E208">
         <v>-0.14777000000000001</v>
@@ -5697,10 +5697,10 @@
         <v>-82.8125</v>
       </c>
       <c r="C209">
-        <v>0.14499000000000001</v>
+        <v>-0.14502999999999999</v>
       </c>
       <c r="D209">
-        <v>82.8125</v>
+        <v>-82.8125</v>
       </c>
       <c r="E209">
         <v>-0.14502999999999999</v>
@@ -5723,10 +5723,10 @@
         <v>-81.25</v>
       </c>
       <c r="C210">
-        <v>0.14227000000000001</v>
+        <v>-0.14230000000000001</v>
       </c>
       <c r="D210">
-        <v>81.25</v>
+        <v>-81.25</v>
       </c>
       <c r="E210">
         <v>-0.14227000000000001</v>
@@ -5749,10 +5749,10 @@
         <v>-79.6875</v>
       </c>
       <c r="C211">
-        <v>0.13950000000000001</v>
+        <v>-0.13954</v>
       </c>
       <c r="D211">
-        <v>79.6875</v>
+        <v>-79.6875</v>
       </c>
       <c r="E211">
         <v>-0.13952000000000001</v>
@@ -5775,10 +5775,10 @@
         <v>-78.125</v>
       </c>
       <c r="C212">
-        <v>0.13675999999999999</v>
+        <v>-0.1368</v>
       </c>
       <c r="D212">
-        <v>78.125</v>
+        <v>-78.125</v>
       </c>
       <c r="E212">
         <v>-0.13675999999999999</v>
@@ -5801,10 +5801,10 @@
         <v>-76.5625</v>
       </c>
       <c r="C213">
-        <v>0.13403000000000001</v>
+        <v>-0.13403000000000001</v>
       </c>
       <c r="D213">
-        <v>76.5625</v>
+        <v>-76.5625</v>
       </c>
       <c r="E213">
         <v>-0.13403000000000001</v>
@@ -5827,10 +5827,10 @@
         <v>-75</v>
       </c>
       <c r="C214">
-        <v>0.13127</v>
+        <v>-0.13128999999999999</v>
       </c>
       <c r="D214">
-        <v>75</v>
+        <v>-75</v>
       </c>
       <c r="E214">
         <v>-0.13127</v>
@@ -5853,10 +5853,10 @@
         <v>-73.4375</v>
       </c>
       <c r="C215">
-        <v>0.12856000000000001</v>
+        <v>-0.12856000000000001</v>
       </c>
       <c r="D215">
-        <v>73.4375</v>
+        <v>-73.4375</v>
       </c>
       <c r="E215">
         <v>-0.12853999999999999</v>
@@ -5879,10 +5879,10 @@
         <v>-71.875</v>
       </c>
       <c r="C216">
-        <v>0.12578</v>
+        <v>-0.1258</v>
       </c>
       <c r="D216">
-        <v>71.875</v>
+        <v>-71.875</v>
       </c>
       <c r="E216">
         <v>-0.12578</v>
@@ -5905,10 +5905,10 @@
         <v>-70.3125</v>
       </c>
       <c r="C217">
-        <v>0.12307</v>
+        <v>-0.12304</v>
       </c>
       <c r="D217">
-        <v>70.3125</v>
+        <v>-70.3125</v>
       </c>
       <c r="E217">
         <v>-0.12304</v>
@@ -5931,10 +5931,10 @@
         <v>-68.75</v>
       </c>
       <c r="C218">
-        <v>0.12031</v>
+        <v>-0.12033000000000001</v>
       </c>
       <c r="D218">
-        <v>68.75</v>
+        <v>-68.75</v>
       </c>
       <c r="E218">
         <v>-0.12028999999999999</v>
@@ -5957,10 +5957,10 @@
         <v>-67.1875</v>
       </c>
       <c r="C219">
-        <v>0.11758</v>
+        <v>-0.11755</v>
       </c>
       <c r="D219">
-        <v>67.1875</v>
+        <v>-67.1875</v>
       </c>
       <c r="E219">
         <v>-0.11755</v>
@@ -5983,10 +5983,10 @@
         <v>-65.625</v>
       </c>
       <c r="C220">
-        <v>0.11484</v>
+        <v>-0.11482000000000001</v>
       </c>
       <c r="D220">
-        <v>65.625</v>
+        <v>-65.625</v>
       </c>
       <c r="E220">
         <v>-0.1148</v>
@@ -6009,10 +6009,10 @@
         <v>-64.0625</v>
       </c>
       <c r="C221">
-        <v>0.11211</v>
+        <v>-0.11206000000000001</v>
       </c>
       <c r="D221">
-        <v>64.0625</v>
+        <v>-64.0625</v>
       </c>
       <c r="E221">
         <v>-0.11206000000000001</v>
@@ -6035,10 +6035,10 @@
         <v>-62.5</v>
       </c>
       <c r="C222">
-        <v>0.10931</v>
+        <v>-0.10931</v>
       </c>
       <c r="D222">
-        <v>62.5</v>
+        <v>-62.5</v>
       </c>
       <c r="E222">
         <v>-0.10928</v>
@@ -6061,10 +6061,10 @@
         <v>-60.9375</v>
       </c>
       <c r="C223">
-        <v>0.10661</v>
+        <v>-0.10657</v>
       </c>
       <c r="D223">
-        <v>60.9375</v>
+        <v>-60.9375</v>
       </c>
       <c r="E223">
         <v>-0.10655000000000001</v>
@@ -6087,10 +6087,10 @@
         <v>-59.375</v>
       </c>
       <c r="C224">
-        <v>0.10384</v>
+        <v>-0.10384</v>
       </c>
       <c r="D224">
-        <v>59.375</v>
+        <v>-59.375</v>
       </c>
       <c r="E224">
         <v>-0.10378999999999999</v>
@@ -6113,10 +6113,10 @@
         <v>-57.8125</v>
       </c>
       <c r="C225">
-        <v>0.10112</v>
+        <v>-0.10108</v>
       </c>
       <c r="D225">
-        <v>57.8125</v>
+        <v>-57.8125</v>
       </c>
       <c r="E225">
         <v>-0.10106</v>
@@ -6139,10 +6139,10 @@
         <v>-56.25</v>
       </c>
       <c r="C226">
-        <v>9.8369999999999999E-2</v>
+        <v>-9.8350000000000007E-2</v>
       </c>
       <c r="D226">
-        <v>56.25</v>
+        <v>-56.25</v>
       </c>
       <c r="E226">
         <v>-9.8320000000000005E-2</v>
@@ -6165,10 +6165,10 @@
         <v>-54.6875</v>
       </c>
       <c r="C227">
-        <v>9.5649999999999999E-2</v>
+        <v>-9.5589999999999994E-2</v>
       </c>
       <c r="D227">
-        <v>54.6875</v>
+        <v>-54.6875</v>
       </c>
       <c r="E227">
         <v>-9.5570000000000002E-2</v>
@@ -6191,10 +6191,10 @@
         <v>-53.125</v>
       </c>
       <c r="C228">
-        <v>9.2899999999999996E-2</v>
+        <v>-9.2850000000000002E-2</v>
       </c>
       <c r="D228">
-        <v>53.125</v>
+        <v>-53.125</v>
       </c>
       <c r="E228">
         <v>-9.2829999999999996E-2</v>
@@ -6217,10 +6217,10 @@
         <v>-51.5625</v>
       </c>
       <c r="C229">
-        <v>9.0160000000000004E-2</v>
+        <v>-9.0120000000000006E-2</v>
       </c>
       <c r="D229">
-        <v>51.5625</v>
+        <v>-51.5625</v>
       </c>
       <c r="E229">
         <v>-9.01E-2</v>
@@ -6243,10 +6243,10 @@
         <v>-50</v>
       </c>
       <c r="C230">
-        <v>8.7340000000000001E-2</v>
+        <v>-8.7279999999999996E-2</v>
       </c>
       <c r="D230">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="E230">
         <v>-8.7279999999999996E-2</v>
@@ -6269,10 +6269,10 @@
         <v>-48.4375</v>
       </c>
       <c r="C231">
-        <v>8.4610000000000005E-2</v>
+        <v>-8.4540000000000004E-2</v>
       </c>
       <c r="D231">
-        <v>48.4375</v>
+        <v>-48.4375</v>
       </c>
       <c r="E231">
         <v>-8.4540000000000004E-2</v>
@@ -6295,10 +6295,10 @@
         <v>-46.875</v>
       </c>
       <c r="C232">
-        <v>8.1850000000000006E-2</v>
+        <v>-8.1790000000000002E-2</v>
       </c>
       <c r="D232">
-        <v>46.875</v>
+        <v>-46.875</v>
       </c>
       <c r="E232">
         <v>-8.1790000000000002E-2</v>
@@ -6321,10 +6321,10 @@
         <v>-45.3125</v>
       </c>
       <c r="C233">
-        <v>7.9140000000000002E-2</v>
+        <v>-7.9030000000000003E-2</v>
       </c>
       <c r="D233">
-        <v>45.3125</v>
+        <v>-45.3125</v>
       </c>
       <c r="E233">
         <v>-7.9049999999999995E-2</v>
@@ -6347,10 +6347,10 @@
         <v>-43.75</v>
       </c>
       <c r="C234">
-        <v>7.6380000000000003E-2</v>
+        <v>-7.6289999999999997E-2</v>
       </c>
       <c r="D234">
-        <v>43.75</v>
+        <v>-43.75</v>
       </c>
       <c r="E234">
         <v>-7.6289999999999997E-2</v>
@@ -6373,10 +6373,10 @@
         <v>-42.1875</v>
       </c>
       <c r="C235">
-        <v>7.3649999999999993E-2</v>
+        <v>-7.356E-2</v>
       </c>
       <c r="D235">
-        <v>42.1875</v>
+        <v>-42.1875</v>
       </c>
       <c r="E235">
         <v>-7.356E-2</v>
@@ -6399,10 +6399,10 @@
         <v>-40.625</v>
       </c>
       <c r="C236">
-        <v>7.0889999999999995E-2</v>
+        <v>-7.0800000000000002E-2</v>
       </c>
       <c r="D236">
-        <v>40.625</v>
+        <v>-40.625</v>
       </c>
       <c r="E236">
         <v>-7.0830000000000004E-2</v>
@@ -6425,10 +6425,10 @@
         <v>-39.0625</v>
       </c>
       <c r="C237">
-        <v>6.8180000000000004E-2</v>
+        <v>-6.8070000000000006E-2</v>
       </c>
       <c r="D237">
-        <v>39.0625</v>
+        <v>-39.0625</v>
       </c>
       <c r="E237">
         <v>-6.8049999999999999E-2</v>
@@ -6451,10 +6451,10 @@
         <v>-37.5</v>
       </c>
       <c r="C238">
-        <v>6.54E-2</v>
+        <v>-6.5310000000000007E-2</v>
       </c>
       <c r="D238">
-        <v>37.5</v>
+        <v>-37.5</v>
       </c>
       <c r="E238">
         <v>-6.497E-2</v>
@@ -6477,10 +6477,10 @@
         <v>-35.9375</v>
       </c>
       <c r="C239">
-        <v>6.2689999999999996E-2</v>
+        <v>-6.2579999999999997E-2</v>
       </c>
       <c r="D239">
-        <v>35.9375</v>
+        <v>-35.9375</v>
       </c>
       <c r="E239">
         <v>-5.9540000000000003E-2</v>
@@ -6503,10 +6503,10 @@
         <v>-34.375</v>
       </c>
       <c r="C240">
-        <v>5.9909999999999998E-2</v>
+        <v>-5.9819999999999998E-2</v>
       </c>
       <c r="D240">
-        <v>34.375</v>
+        <v>-34.375</v>
       </c>
       <c r="E240">
         <v>-1.094E-2</v>
@@ -6529,10 +6529,10 @@
         <v>-32.8125</v>
       </c>
       <c r="C241">
-        <v>5.7169999999999999E-2</v>
+        <v>-5.706E-2</v>
       </c>
       <c r="D241">
-        <v>32.8125</v>
+        <v>-32.8125</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -6555,10 +6555,10 @@
         <v>-31.25</v>
       </c>
       <c r="C242">
-        <v>5.416E-2</v>
+        <v>-5.4179999999999999E-2</v>
       </c>
       <c r="D242">
-        <v>31.25</v>
+        <v>-31.25</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -6581,10 +6581,10 @@
         <v>-29.6875</v>
       </c>
       <c r="C243">
-        <v>5.0070000000000003E-2</v>
+        <v>-5.0650000000000001E-2</v>
       </c>
       <c r="D243">
-        <v>29.6875</v>
+        <v>-29.6875</v>
       </c>
       <c r="E243">
         <v>0</v>
@@ -6607,10 +6607,10 @@
         <v>-28.125</v>
       </c>
       <c r="C244">
-        <v>4.3580000000000001E-2</v>
+        <v>-4.5289999999999997E-2</v>
       </c>
       <c r="D244">
-        <v>28.125</v>
+        <v>-28.125</v>
       </c>
       <c r="E244">
         <v>0</v>
@@ -6633,10 +6633,10 @@
         <v>-26.5625</v>
       </c>
       <c r="C245">
-        <v>1.3440000000000001E-2</v>
+        <v>-3.6799999999999999E-2</v>
       </c>
       <c r="D245">
-        <v>26.5625</v>
+        <v>-26.5625</v>
       </c>
       <c r="E245">
         <v>0</v>
@@ -6659,10 +6659,10 @@
         <v>-25</v>
       </c>
       <c r="C246">
-        <v>0</v>
+        <v>-5.1000000000000004E-3</v>
       </c>
       <c r="D246">
-        <v>25</v>
+        <v>-25</v>
       </c>
       <c r="E246">
         <v>0</v>
@@ -6688,7 +6688,7 @@
         <v>0</v>
       </c>
       <c r="D247">
-        <v>23.4375</v>
+        <v>-23.4375</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -6714,7 +6714,7 @@
         <v>0</v>
       </c>
       <c r="D248">
-        <v>21.875</v>
+        <v>-21.875</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -6740,7 +6740,7 @@
         <v>0</v>
       </c>
       <c r="D249">
-        <v>20.3125</v>
+        <v>-20.3125</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -6766,7 +6766,7 @@
         <v>0</v>
       </c>
       <c r="D250">
-        <v>18.75</v>
+        <v>-18.75</v>
       </c>
       <c r="E250">
         <v>0</v>
@@ -6792,7 +6792,7 @@
         <v>0</v>
       </c>
       <c r="D251">
-        <v>17.1875</v>
+        <v>-17.1875</v>
       </c>
       <c r="E251">
         <v>0</v>
@@ -6818,7 +6818,7 @@
         <v>0</v>
       </c>
       <c r="D252">
-        <v>15.625</v>
+        <v>-15.625</v>
       </c>
       <c r="E252">
         <v>0</v>
@@ -6844,7 +6844,7 @@
         <v>0</v>
       </c>
       <c r="D253">
-        <v>14.0625</v>
+        <v>-14.0625</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -6870,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="D254">
-        <v>12.5</v>
+        <v>-12.5</v>
       </c>
       <c r="E254">
         <v>0</v>
@@ -6896,7 +6896,7 @@
         <v>0</v>
       </c>
       <c r="D255">
-        <v>10.9375</v>
+        <v>-10.9375</v>
       </c>
       <c r="E255">
         <v>0</v>
@@ -6922,7 +6922,7 @@
         <v>0</v>
       </c>
       <c r="D256">
-        <v>9.375</v>
+        <v>-9.375</v>
       </c>
       <c r="E256">
         <v>0</v>
@@ -6948,7 +6948,7 @@
         <v>0</v>
       </c>
       <c r="D257">
-        <v>7.8125</v>
+        <v>-7.8125</v>
       </c>
       <c r="E257">
         <v>0</v>
@@ -6974,7 +6974,7 @@
         <v>0</v>
       </c>
       <c r="D258">
-        <v>6.25</v>
+        <v>-6.25</v>
       </c>
       <c r="E258">
         <v>0</v>
@@ -7000,7 +7000,7 @@
         <v>0</v>
       </c>
       <c r="D259">
-        <v>4.6875</v>
+        <v>-4.6875</v>
       </c>
       <c r="E259">
         <v>0</v>
@@ -7026,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="D260">
-        <v>3.125</v>
+        <v>-3.125</v>
       </c>
       <c r="E260">
         <v>0</v>
@@ -7052,7 +7052,7 @@
         <v>0</v>
       </c>
       <c r="D261">
-        <v>1.5625</v>
+        <v>-1.5625</v>
       </c>
       <c r="E261">
         <v>0</v>
